--- a/output/pdf_financials_xlsx/HMCC.P.xlsx
+++ b/output/pdf_financials_xlsx/HMCC.P.xlsx
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.059882</v>
+        <v>-0.059882</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.019496</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.028038</v>
+        <v>-0.028038</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.014783</v>
+        <v>-0.014783</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.017253</v>
+        <v>-0.017253</v>
       </c>
     </row>
     <row r="17">
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.059882</v>
+        <v>-0.059882</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.019496</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.028038</v>
+        <v>-0.028038</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.014783</v>
+        <v>-0.014783</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.017253</v>
+        <v>-0.017253</v>
       </c>
     </row>
     <row r="21">
@@ -1037,19 +1037,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.059882</v>
+        <v>-0.059882</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.019496</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.028038</v>
+        <v>-0.028038</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.014783</v>
+        <v>-0.014783</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.017253</v>
+        <v>-0.017253</v>
       </c>
     </row>
     <row r="24">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.059882</v>
+        <v>-0.059882</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.019496</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.028038</v>
+        <v>-0.028038</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.014783</v>
+        <v>-0.014783</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.017253</v>
+        <v>-0.017253</v>
       </c>
     </row>
     <row r="28">
@@ -1209,19 +1209,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.059882</v>
+        <v>-0.059882</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.019496</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.028038</v>
+        <v>-0.028038</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.014783</v>
+        <v>-0.014783</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.017253</v>
+        <v>-0.017253</v>
       </c>
     </row>
     <row r="30">
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3493,10 +3493,10 @@
         <v>-0.059882</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.028038</v>
+        <v>-0.028038</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.014783</v>
+        <v>-0.014783</v>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
@@ -6291,13 +6291,13 @@
         </is>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0.028038</v>
+        <v>-0.028038</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>0.014783</v>
+        <v>-0.014783</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>0.017253</v>
+        <v>-0.017253</v>
       </c>
     </row>
     <row r="38">
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.059882</v>
+        <v>-0.059882</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/HMCC.P.xlsx
+++ b/output/pdf_financials_xlsx/HMCC.P.xlsx
@@ -672,10 +672,10 @@
         <v>0.007291</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.003158</v>
+        <v>0.028038</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.002286</v>
+        <v>0.022084</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.002263</v>
@@ -699,10 +699,10 @@
         <v>-0.007291</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.003158</v>
+        <v>-0.028038</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.002286</v>
+        <v>-0.022084</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-0.002263</v>
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.297766</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.269375</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.297766</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.269375</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">

--- a/output/pdf_financials_xlsx/HMCC.P.xlsx
+++ b/output/pdf_financials_xlsx/HMCC.P.xlsx
@@ -1344,25 +1344,19 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.297766</v>
+        <v>0.269375</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.269375</v>
       </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E34" s="3" t="n">
+        <v>0.213987</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.198191</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.181333</v>
       </c>
     </row>
     <row r="35">
@@ -1382,20 +1376,14 @@
       <c r="D35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1410,25 +1398,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.297766</v>
+        <v>0.269375</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.269375</v>
       </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E36" s="3" t="n">
+        <v>0.213987</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0.198191</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.181333</v>
       </c>
     </row>
     <row r="37">
@@ -1448,20 +1430,14 @@
       <c r="D37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1481,20 +1457,14 @@
       <c r="D38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1514,20 +1484,14 @@
       <c r="D39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1547,20 +1511,14 @@
       <c r="D40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1580,20 +1538,14 @@
       <c r="D41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1613,20 +1565,14 @@
       <c r="D42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1646,20 +1592,14 @@
       <c r="D43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1679,20 +1619,14 @@
       <c r="D44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1712,20 +1646,14 @@
       <c r="D45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1745,20 +1673,14 @@
       <c r="D46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1778,20 +1700,14 @@
       <c r="D47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1811,20 +1727,14 @@
       <c r="D48" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1881,20 +1791,14 @@
       <c r="D50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1914,20 +1818,14 @@
       <c r="D51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1947,20 +1845,14 @@
       <c r="D52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1980,20 +1872,14 @@
       <c r="D53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2013,20 +1899,14 @@
       <c r="D54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2083,20 +1963,14 @@
       <c r="D56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2116,20 +1990,14 @@
       <c r="D57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2149,20 +2017,14 @@
       <c r="D58" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2182,20 +2044,14 @@
       <c r="D59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2215,20 +2071,14 @@
       <c r="D60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2248,20 +2098,14 @@
       <c r="D61" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2313,25 +2157,19 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>0.297766</v>
+        <v>0.269375</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>0.269375</v>
       </c>
-      <c r="E63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E63" s="3" t="n">
+        <v>0.213987</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>0.198191</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0.181333</v>
       </c>
     </row>
     <row r="64">
@@ -2351,20 +2189,14 @@
       <c r="D64" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2384,20 +2216,14 @@
       <c r="D65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2417,20 +2243,14 @@
       <c r="D66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2450,20 +2270,14 @@
       <c r="D67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2478,25 +2292,19 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.007997000000000001</v>
+        <v>0.038893</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>0.038893</v>
       </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E68" s="3" t="n">
+        <v>0.011544</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0.010532</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0.010927</v>
       </c>
     </row>
     <row r="69">
@@ -2516,20 +2324,14 @@
       <c r="D69" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2549,20 +2351,14 @@
       <c r="D70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2582,20 +2378,14 @@
       <c r="D71" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2615,20 +2405,14 @@
       <c r="D72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2648,20 +2432,14 @@
       <c r="D73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2681,20 +2459,14 @@
       <c r="D74" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2714,20 +2486,14 @@
       <c r="D75" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2784,20 +2550,14 @@
       <c r="D77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2817,20 +2577,14 @@
       <c r="D78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2850,20 +2604,14 @@
       <c r="D79" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2920,20 +2668,14 @@
       <c r="D81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2953,20 +2695,14 @@
       <c r="D82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2986,20 +2722,14 @@
       <c r="D83" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3019,20 +2749,14 @@
       <c r="D84" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3052,20 +2776,14 @@
       <c r="D85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3117,25 +2835,19 @@
         </is>
       </c>
       <c r="C87" s="3" t="n">
-        <v>0.007997000000000001</v>
+        <v>0.038893</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>0.038893</v>
       </c>
-      <c r="E87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E87" s="3" t="n">
+        <v>0.011544</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0.010532</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0.010927</v>
       </c>
     </row>
     <row r="88">
@@ -3150,25 +2862,19 @@
         </is>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0.334282</v>
+        <v>0.356577</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>0.356577</v>
       </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E88" s="3" t="n">
+        <v>0.356577</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.356577</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0.356577</v>
       </c>
     </row>
     <row r="89">
@@ -3188,20 +2894,14 @@
       <c r="D89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -3221,20 +2921,14 @@
       <c r="D90" s="3" t="n">
         <v>-0.178525</v>
       </c>
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E90" s="3" t="n">
+        <v>-0.206564</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>-0.221348</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>-0.238601</v>
       </c>
     </row>
     <row r="91">
@@ -3254,20 +2948,14 @@
       <c r="D91" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -3287,20 +2975,14 @@
       <c r="D92" s="3" t="n">
         <v>0.05243</v>
       </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E92" s="3" t="n">
+        <v>0.05243</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0.05243</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0.05243</v>
       </c>
     </row>
     <row r="93">
@@ -3320,20 +3002,14 @@
       <c r="D93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -3348,25 +3024,19 @@
         </is>
       </c>
       <c r="C94" s="3" t="n">
-        <v>0.289769</v>
+        <v>0.230482</v>
       </c>
       <c r="D94" s="3" t="n">
         <v>0.230482</v>
       </c>
-      <c r="E94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E94" s="3" t="n">
+        <v>0.202443</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0.187659</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>0.170406</v>
       </c>
     </row>
     <row r="95">
@@ -3386,20 +3056,14 @@
       <c r="D95" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3414,25 +3078,19 @@
         </is>
       </c>
       <c r="C96" s="3" t="n">
-        <v>0.289769</v>
+        <v>0.230482</v>
       </c>
       <c r="D96" s="3" t="n">
         <v>0.230482</v>
       </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E96" s="3" t="n">
+        <v>0.202443</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0.187659</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>0.170406</v>
       </c>
     </row>
     <row r="97">
@@ -3447,25 +3105,19 @@
         </is>
       </c>
       <c r="C97" s="3" t="n">
-        <v>0.9731433407440742</v>
+        <v>0.8556176334106729</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>0.8556176334106729</v>
       </c>
-      <c r="E97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E97" s="3" t="n">
+        <v>0.9460527975998542</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>0.946859342755221</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0.9397406980527537</v>
       </c>
     </row>
     <row r="98">
@@ -3498,10 +3150,8 @@
       <c r="F99" s="3" t="n">
         <v>-0.014783</v>
       </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G99" s="3" t="n">
+        <v>-0.017253</v>
       </c>
     </row>
     <row r="100">
@@ -3527,10 +3177,8 @@
       <c r="F100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -3556,10 +3204,8 @@
       <c r="F101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3585,10 +3231,8 @@
       <c r="F102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3614,10 +3258,8 @@
       <c r="F103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3643,10 +3285,8 @@
       <c r="F104" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G104" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -3672,10 +3312,8 @@
       <c r="F105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3701,10 +3339,8 @@
       <c r="F106" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G106" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -3730,10 +3366,8 @@
       <c r="F107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3759,10 +3393,8 @@
       <c r="F108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3788,10 +3420,8 @@
       <c r="F109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3817,10 +3447,8 @@
       <c r="F110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3846,10 +3474,8 @@
       <c r="F111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3875,10 +3501,8 @@
       <c r="F112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3904,10 +3528,8 @@
       <c r="F113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3933,10 +3555,8 @@
       <c r="F114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3962,10 +3582,8 @@
       <c r="F115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3991,10 +3609,8 @@
       <c r="F116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -4020,10 +3636,8 @@
       <c r="F117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -4049,10 +3663,8 @@
       <c r="F118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -4113,10 +3725,8 @@
       <c r="F120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -4142,10 +3752,8 @@
       <c r="F121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -4171,10 +3779,8 @@
       <c r="F122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -4200,10 +3806,8 @@
       <c r="F123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -4229,10 +3833,8 @@
       <c r="F124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -4258,10 +3860,8 @@
       <c r="F125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -4287,10 +3887,8 @@
       <c r="F126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -4353,10 +3951,8 @@
       <c r="F128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -4417,10 +4013,8 @@
       <c r="F130" s="3" t="n">
         <v>0.213987</v>
       </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G130" s="3" t="n">
+        <v>0.198191</v>
       </c>
     </row>
     <row r="131">
@@ -4446,10 +4040,8 @@
       <c r="F131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -4475,10 +4067,8 @@
       <c r="F132" s="3" t="n">
         <v>-0.015796</v>
       </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G132" s="3" t="n">
+        <v>-0.016858</v>
       </c>
     </row>
     <row r="133">
@@ -4504,10 +4094,8 @@
       <c r="F133" s="3" t="n">
         <v>0.198191</v>
       </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G133" s="3" t="n">
+        <v>0.181333</v>
       </c>
     </row>
     <row r="134">
@@ -4533,10 +4121,8 @@
       <c r="F134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -4562,10 +4148,8 @@
       <c r="F135" s="3" t="n">
         <v>-0.015796</v>
       </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G135" s="3" t="n">
+        <v>-0.016858</v>
       </c>
     </row>
   </sheetData>
@@ -4579,7 +4163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4653,7 +4237,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cash 5</t>
+          <t>Cash and cash equivalents 5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4666,26 +4250,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="5" t="n">
-        <v>0.297766</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.269375</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0.213987</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>0.198191</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>0.181333</v>
       </c>
     </row>
     <row r="3">
@@ -4720,20 +4302,14 @@
       <c r="G3" s="5" t="n">
         <v>0.269375</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H3" s="5" t="n">
+        <v>0.213987</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0.198191</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0.181333</v>
       </c>
     </row>
     <row r="4">
@@ -4742,7 +4318,11 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LIABILITIES</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Accounts payable and accruals 10</t>
@@ -4758,26 +4338,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
-        <v>0.007997000000000001</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.038893</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.011544</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0.010532</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0.010927</v>
       </c>
     </row>
     <row r="5">
@@ -4812,20 +4390,14 @@
       <c r="G5" s="5" t="n">
         <v>0.356577</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H5" s="5" t="n">
+        <v>0.356577</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0.356577</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0.356577</v>
       </c>
     </row>
     <row r="6">
@@ -4841,37 +4413,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Warrants 6</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Contributed surplus 6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>0.0217</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H6" s="5" t="n">
+        <v>0.05243</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0.05243</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0.05243</v>
       </c>
     </row>
     <row r="7">
@@ -4887,12 +4459,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Contributed Surplus 6</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AdditionalPaidInCapital</t>
+          <t>RetainedEarnings</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4901,25 +4473,19 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.05243</v>
+        <v>-0.118643</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.05243</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.178525</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>-0.206564</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>-0.221348</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>-0.238601</v>
       </c>
     </row>
     <row r="8">
@@ -4935,12 +4501,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>TOTAL SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4949,25 +4515,19 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.118643</v>
+        <v>0.289769</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.178525</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.230482</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.202443</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0.187659</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.170406</v>
       </c>
     </row>
     <row r="9">
@@ -4983,12 +4543,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TOTAL SHAREHOLDERS’ EQUITY</t>
+          <t>TOTAL LIABILITIES AND SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4997,25 +4557,19 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.289769</v>
+        <v>0.297766</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.230482</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.269375</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.213987</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0.198191</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0.181333</v>
       </c>
     </row>
     <row r="10">
@@ -5024,31 +4578,25 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TOTAL LIABILITIES AND SHAREHOLDERS' EQUITY</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
+          <t>As at December</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.297766</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>0.269375</v>
+        <v>3.1e-05</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -5069,40 +4617,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITES                            Notes</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Cash 5 213,987</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F11" s="5" t="n">
+        <v>0.269375</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n">
-        <v>-0.028039</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>-0.014784</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5113,40 +4667,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITES                            Notes</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Change in accounts payable and accruals</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>TOTAL ASSETS 213,987</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F12" s="5" t="n">
+        <v>0.269375</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n">
-        <v>-0.027349</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>-0.001012</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5157,22 +4717,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITES                            Notes</t>
+          <t>LIABILITIES</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cash flow used in operating activities</t>
+          <t>Accounts payable and accruals 10 11,544</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5180,21 +4740,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F13" s="5" t="n">
+        <v>0.038893</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n">
-        <v>-0.055388</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>-0.015796</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5205,22 +4767,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITES                            Notes</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Decrease in cash and cash equivalents</t>
+          <t>Share capital 6 356,577</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5228,21 +4790,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F14" s="5" t="n">
+        <v>0.356577</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>-0.055388</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>-0.015796</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5253,22 +4817,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITES                            Notes</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
+          <t>Contributed Surplus 6 52,430</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5276,21 +4840,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F15" s="5" t="n">
+        <v>0.05243</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n">
-        <v>0.269375</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>0.213987</v>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5301,44 +4867,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITES                            Notes</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Deficit (206,564)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F16" s="5" t="n">
+        <v>-0.178525</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n">
-        <v>0.213987</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>0.198191</v>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5349,36 +4913,46 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Description of the Business</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The address of the Corporation’s registered office is 800, 333 – 7th Avenue S.W., Calgary, AB T2P 2Z1. a resolution of the Directors on April</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>TOTAL SHAREHOLDERS’ EQUITY 202,443</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>0.002025</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>2.2e-05</v>
+        <v>0.230482</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5389,35 +4963,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OPERATIONS                                     Notes</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>TOTAL LIABILITIES AND SHAREHOLDERS' EQUITY 213,987</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>-0.059882</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>-0.028039</v>
+      <c r="F18" s="5" t="n">
+        <v>0.269375</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -5433,17 +5013,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OPERATIONS                                     Notes</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Change in accounts payable and accruals</t>
+          <t>Nature of organization</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -5452,16 +5032,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>0.030896</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>-0.027349</v>
+      <c r="F19" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -5477,39 +5059,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OPERATIONS                                     Notes</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cash flow used in operating activities</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Letter of intent</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-0.028985</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>-0.055388</v>
+      <c r="F20" s="5" t="n">
+        <v>1.1e-05</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -5525,32 +5105,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FINANCING</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Share issue costs refunded 6</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Cash 5</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F21" s="5" t="n">
+        <v>0.297766</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.000595</v>
+        <v>0.269375</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -5571,22 +5153,18 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>FINANCING</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cash flow provided by financing activities</t>
+          <t>Accounts payable and accruals 10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -5594,13 +5172,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F22" s="5" t="n">
+        <v>0.007997000000000001</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.000595</v>
+        <v>0.038893</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -5621,37 +5197,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FINANCING</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Decrease in cash</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Warrants 6</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-0.022645</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>-0.028391</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>-0.055388</v>
+        <v>0.0217</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -5667,22 +5243,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FINANCING</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Contributed Surplus 6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -5690,16 +5266,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F24" s="5" t="n">
+        <v>0.05243</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.297766</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>0.269375</v>
+        <v>0.05243</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -5720,19 +5296,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FINANCING</t>
+          <t>OPERATIONS                                    Notes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -5743,21 +5315,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n">
-        <v>0.269375</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>0.213987</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>-0.014784</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>-0.017253</v>
       </c>
     </row>
     <row r="26">
@@ -5768,12 +5340,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2.  Basis of Preparation</t>
+          <t>OPERATIONS                                    Notes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Reporting Standards (“IFRS”), as issued by the International Accounting Standards Board (“IASB”) and in effect on January</t>
+          <t>Change in accounts payable and accruals</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -5782,24 +5354,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F26" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>-0.001012</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>0.000395</v>
       </c>
     </row>
     <row r="27">
@@ -5810,17 +5384,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OPERATIONS                                Notes</t>
+          <t>OPERATIONS                                    Notes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Cash flow used in operating activities</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5828,26 +5402,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F27" s="5" t="n">
-        <v>-0.019496</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>-0.059882</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="5" t="n">
+        <v>-0.015796</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>-0.016858</v>
       </c>
     </row>
     <row r="28">
@@ -5858,40 +5432,44 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OPERATIONS                                Notes</t>
+          <t>OPERATIONS                                    Notes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Change in accounts payable and accruals</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Decrease in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F28" s="5" t="n">
-        <v>-0.003149</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0.030896</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="5" t="n">
+        <v>-0.015796</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>-0.016858</v>
       </c>
     </row>
     <row r="29">
@@ -5902,17 +5480,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OPERATIONS                                Notes</t>
+          <t>OPERATIONS                                    Notes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cash flow used in operating activities</t>
+          <t>Cash and cash equivalents, beginning of year</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5920,26 +5498,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F29" s="5" t="n">
-        <v>-0.022645</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>-0.028986</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="5" t="n">
+        <v>0.213987</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>0.198191</v>
       </c>
     </row>
     <row r="30">
@@ -5950,17 +5528,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FINANCING</t>
+          <t>OPERATIONS                                    Notes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
+          <t>Cash and cash equivalents, end of year</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5968,26 +5546,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F30" s="5" t="n">
-        <v>0.320411</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.297766</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="5" t="n">
+        <v>0.198191</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>0.181333</v>
       </c>
     </row>
     <row r="31">
@@ -5998,39 +5576,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FINANCING</t>
+          <t>OPERATING ACTIVITES                            Notes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cash, end of period</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F31" s="5" t="n">
-        <v>0.297766</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.269375</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>-0.028039</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>-0.014784</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -6041,17 +5615,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>OPERATING ACTIVITES                            Notes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Interest income and fair value change</t>
+          <t>Change in accounts payable and accruals</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -6070,37 +5644,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H32" s="5" t="n">
+        <v>-0.027349</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>0.004624</v>
+        <v>-0.001012</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OPERATING ACTIVITES                            Notes</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Cash flow used in operating activities</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -6118,37 +5692,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H33" s="5" t="n">
+        <v>-0.055388</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>0.013427</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>0.013504</v>
+        <v>-0.015796</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OPERATING ACTIVITES                            Notes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Shareholder communications</t>
+          <t>Decrease in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -6156,39 +5730,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F34" s="5" t="n">
-        <v>0.002789</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0.007291</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0.003158</v>
+        <v>-0.055388</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0.002286</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>0.002263</v>
+        <v>-0.015796</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OPERATING ACTIVITES                            Notes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Regulatory</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -6199,38 +5783,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n">
-        <v>0.006772</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0.005913</v>
+        <v>0.269375</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>0.00584</v>
-      </c>
-      <c r="J35" s="5" t="n">
-        <v>0.005808</v>
+        <v>0.213987</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OPERATING ACTIVITES                            Notes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Cash and cash equivalents, end of year</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6238,89 +5826,85 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F36" s="5" t="n">
-        <v>0.000378</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0.00278</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0.000316</v>
+        <v>0.213987</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>0.00053</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>0.000302</v>
+        <v>0.198191</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Description of the Business</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LOSS AND COMPREHENSIVE LOSS FOR THE YEAR</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>The address of the Corporation’s registered office is 800, 333 – 7th Avenue S.W., Calgary, AB T2P 2Z1. a resolution of the Directors on April</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F37" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.002024</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>-0.028038</v>
+        <v>0.002025</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>-0.014783</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>-0.017253</v>
+        <v>2.2e-05</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OPERATIONS                                     Notes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LOSS PER SHARE - Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -6331,35 +5915,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G38" s="5" t="n">
+        <v>-0.059882</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="5" t="n">
-        <v>0</v>
+        <v>-0.028039</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OPERATIONS                                     Notes</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES 6</t>
+          <t>Change in accounts payable and accruals</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -6373,38 +5959,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G39" s="5" t="n">
+        <v>0.030896</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J39" s="5" t="n">
-        <v>5.7</v>
+        <v>-0.027349</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>OPERATIONS                                     Notes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2023 5,700,000 356,577 52,430</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Cash flow used in operating activities</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -6415,42 +6007,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G40" s="5" t="n">
+        <v>-0.028985</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>0.202443</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>0.202443</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>-0.206564</v>
+        <v>-0.055388</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss - - -</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share issue costs refunded 6</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -6461,38 +6051,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>-0.028038</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>-0.014784</v>
-      </c>
-      <c r="J41" s="5" t="n">
-        <v>-0.014784</v>
+      <c r="G41" s="5" t="n">
+        <v>0.000595</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2024 5,700,000 356,577 52,430</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Cash flow provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -6503,84 +6101,90 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>0.187659</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>0.187659</v>
-      </c>
-      <c r="J42" s="5" t="n">
-        <v>-0.221348</v>
+      <c r="G42" s="5" t="n">
+        <v>0.000595</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2025 5,700,000 356,577 52,430</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Decrease in cash</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>0.170406</v>
-      </c>
-      <c r="J43" s="5" t="n">
-        <v>-0.238601</v>
+      <c r="F43" s="5" t="n">
+        <v>-0.022645</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>-0.028391</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>-0.055388</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Professional fees 10</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6588,17 +6192,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>0.016329</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.043039</v>
+        <v>0.297766</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.018652</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>0.013427</v>
+        <v>0.269375</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -6609,22 +6217,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>Cash, end of year</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6637,16 +6245,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G45" s="5" t="n">
+        <v>0.269375</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.028038</v>
-      </c>
-      <c r="I45" s="5" t="n">
-        <v>0.022084</v>
+        <v>0.213987</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -6657,17 +6265,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>2.  Basis of Preparation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2022 5,700,000 356,577 52,430</t>
+          <t>Reporting Standards (“IFRS”), as issued by the International Accounting Standards Board (“IASB”) and in effect on January</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -6676,21 +6284,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F46" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.002023</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0.230482</v>
-      </c>
-      <c r="I46" s="5" t="n">
-        <v>-0.178525</v>
+        <v>1e-06</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -6701,28 +6307,34 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>OPERATIONS                                Notes</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>For the years ended December</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.019496</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.059882</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -6743,36 +6355,30 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OPERATIONS                                Notes</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Professional fees 10 18,652</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Change in accounts payable and accruals</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.048499</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.003149</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.030896</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -6793,22 +6399,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OPERATIONS                                Notes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Shareholder communications 3,158</t>
+          <t>Cash flow used in operating activities</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6817,12 +6423,10 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.007291</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.022645</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>-0.028986</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -6843,32 +6447,34 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Regulatory 5,913</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.001313</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.320411</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.297766</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -6889,22 +6495,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>General and administrative 316</t>
+          <t>Cash, end of period</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6913,12 +6519,10 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.00278</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.297766</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.269375</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -6944,26 +6548,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LOSS AND COMPREHENSIVE LOSS FOR THE YEAR 28,039</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Interest income and fair value change</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="5" t="n">
-        <v>-0.059882</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6975,15 +6577,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="5" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0.004624</v>
       </c>
     </row>
     <row r="53">
@@ -6999,17 +6597,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LOSS PER SHARE - Basic and diluted 0.00</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F53" s="5" t="n">
-        <v>1e-08</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -7021,15 +6625,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="5" t="n">
+        <v>0.013427</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>0.013504</v>
       </c>
     </row>
     <row r="54">
@@ -7045,37 +6645,33 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES 6 5,700,000</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Shareholder communications</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002789</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.007291</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0.003158</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0.002286</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0.002263</v>
       </c>
     </row>
     <row r="55">
@@ -7086,12 +6682,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2021 5,700,000 334,282 21,700 52,430 (118,643)</t>
+          <t>Regulatory</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -7100,28 +6696,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F55" s="5" t="n">
-        <v>0.289769</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.006772</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0.005913</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>0.00584</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0.005808</v>
       </c>
     </row>
     <row r="56">
@@ -7132,44 +6722,38 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Warrant expiry (Note 6) - 21,700 (21,700) - -</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F56" s="5" t="n">
+        <v>0.000378</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.00278</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0.000316</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0.00053</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0.000302</v>
       </c>
     </row>
     <row r="57">
@@ -7180,42 +6764,42 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Share issue costs refunded</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>(Note 6) 595 - - -</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>LOSS AND COMPREHENSIVE LOSS FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F57" s="5" t="n">
-        <v>0.000595</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H57" s="5" t="n">
+        <v>-0.028038</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>-0.014783</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>-0.017253</v>
       </c>
     </row>
     <row r="58">
@@ -7226,42 +6810,42 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Share issue costs refunded</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss - - - - (59,882)</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>LOSS PER SHARE - Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F58" s="5" t="n">
-        <v>-0.059882</v>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -7272,12 +6856,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Share issue costs refunded</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2022 5,700,000 356,577 - 52,430 (178,525)</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES 6</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -7286,28 +6870,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F59" s="5" t="n">
-        <v>0.230482</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H59" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>5.7</v>
       </c>
     </row>
     <row r="60">
@@ -7318,12 +6898,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Share issue costs refunded</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss - - - - (23,039)</t>
+          <t>Balance at December 31, 2023 5,700,000 356,577 52,430</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -7332,28 +6912,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F60" s="5" t="n">
-        <v>-0.028038</v>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H60" s="5" t="n">
+        <v>0.202443</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>0.202443</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>-0.206564</v>
       </c>
     </row>
     <row r="61">
@@ -7364,42 +6940,42 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Share issue costs refunded</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2023 5,700,000 356,577 - 52,430 (206,564)</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Loss and comprehensive loss - - -</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F61" s="5" t="n">
-        <v>0.202443</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H61" s="5" t="n">
+        <v>-0.028038</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>-0.014784</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>-0.014784</v>
       </c>
     </row>
     <row r="62">
@@ -7410,12 +6986,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS FOR</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>THE PERIOD</t>
+          <t>Balance at December 31, 2024 5,700,000 356,577 52,430</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -7424,26 +7000,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F62" s="5" t="n">
-        <v>0.019496</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.059882</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0.187659</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>0.187659</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>-0.221348</v>
       </c>
     </row>
     <row r="63">
@@ -7454,44 +7028,40 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS FOR</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NET LOSS PER SHARE - Basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Balance at December 31, 2025 5,700,000 356,577 52,430</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>1e-08</v>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="5" t="n">
+        <v>0.170406</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>-0.238601</v>
       </c>
     </row>
     <row r="64">
@@ -7502,35 +7072,35 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS FOR</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES 6</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Professional fees 10</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>3.5</v>
+        <v>0.016329</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.043039</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>0.018652</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>0.013427</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -7546,35 +7116,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Balance at December 31,</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Balance at December 31,</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F65" s="5" t="n">
-        <v>0.309265</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>-0.099147</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>0.028038</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>0.022084</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -7590,39 +7164,35 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Balance at December 31,</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Net loss - - - -</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance at December 31, 2022 5,700,000 356,577 52,430</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F66" s="5" t="n">
-        <v>-0.019496</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>-0.019496</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>0.230482</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>-0.178525</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -7636,14 +7206,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Balance at December 31,</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Warrant expiry (Note 6) - 21,700 (21,700) -</t>
+          <t>For the years ended December</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -7652,10 +7218,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F67" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -7686,39 +7250,977 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Professional fees 10 18,652</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.048499</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Shareholder communications 3,158</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0.007291</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Regulatory 5,913</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>0.001313</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>General and administrative 316</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>0.00278</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>LOSS AND COMPREHENSIVE LOSS FOR THE YEAR 28,039</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>-0.059882</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>LOSS PER SHARE - Basic and diluted 0.00</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES 6 5,700,000</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Balance at December 31, 2021 5,700,000 334,282 21,700 52,430 (118,643)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>0.289769</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Warrant expiry (Note 6) - 21,700 (21,700) - -</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Share issue costs refunded</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>(Note 6) 595 - - -</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>0.000595</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Share issue costs refunded</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss - - - - (59,882)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>-0.059882</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Share issue costs refunded</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Balance at December 31, 2022 5,700,000 356,577 - 52,430 (178,525)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0.230482</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Share issue costs refunded</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss - - - - (23,039)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>-0.028038</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Share issue costs refunded</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Balance at December 31, 2023 5,700,000 356,577 - 52,430 (206,564)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0.202443</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>NET LOSS AND COMPREHENSIVE LOSS FOR</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>THE PERIOD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0.019496</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.059882</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>NET LOSS AND COMPREHENSIVE LOSS FOR</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>NET LOSS PER SHARE - Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NET LOSS AND COMPREHENSIVE LOSS FOR</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES 6</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>Balance at December 31,</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Balance at December 31,</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0.309265</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>-0.099147</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Balance at December 31,</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Net loss - - - -</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>-0.019496</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>-0.019496</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Balance at December 31,</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Warrant expiry (Note 6) - 21,700 (21,700) -</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Balance at December 31,</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
         <is>
           <t>Share issue costs refunded 595 - -</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="n">
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
         <v>0.000595</v>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
